--- a/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,97</t>
+          <t>-0,82; 11,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 0,0</t>
+          <t>-5,86; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 8,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,96</t>
+          <t>0,23; 7,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,37</t>
+          <t>-0,62; 5,01</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,18</t>
+          <t>0,44; 5,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,08</t>
+          <t>0,98; 6,8</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,22</t>
+          <t>-1,82; 9,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,0</t>
+          <t>-7,54; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,85</t>
+          <t>-0,39; 7,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,43</t>
+          <t>-1,45; 4,57</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,33</t>
+          <t>-0,54; 5,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,44</t>
+          <t>-0,03; 6,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,63</t>
+          <t>-4,2; 1,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,93</t>
+          <t>-3,3; 2,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,27</t>
+          <t>-1,6; 2,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,24</t>
+          <t>-0,86; 3,47</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,0; 658,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 881,07</t>
+          <t>-63,72; 1154,81</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 3,88</t>
+          <t>-3,97; 3,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,28</t>
+          <t>-2,28; 6,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,16</t>
+          <t>0,87; 8,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,73</t>
+          <t>-0,53; 4,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,46</t>
+          <t>-0,7; 4,37</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,0</t>
+          <t>-9,01; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 0,0</t>
+          <t>-9,13; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,86</t>
+          <t>0,43; 3,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,7</t>
+          <t>0,47; 3,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,45</t>
+          <t>-0,38; 2,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,16</t>
+          <t>-0,56; 2,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,49</t>
+          <t>0,47; 2,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,35</t>
+          <t>0,33; 2,39</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,5; inf</t>
+          <t>-0,59; 2006,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 1680,79</t>
+          <t>-18,3; 1834,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 829,46</t>
+          <t>-51,88; 691,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 628,94</t>
+          <t>-62,26; 739,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26,0; 661,02</t>
+          <t>29,99; 686,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,47; 663,69</t>
+          <t>14,89; 590,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 11,52</t>
+          <t>-0,71; 12,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,0</t>
+          <t>-5,79; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,0</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,54</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,26</t>
+          <t>0,1; 7,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,01</t>
+          <t>-0,73; 4,41</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,38</t>
+          <t>0,44; 5,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,8</t>
+          <t>0,68; 7,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 10,33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,64</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 9,82</t>
+          <t>-1,84; 10,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,0</t>
+          <t>-5,24; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 7,21</t>
+          <t>-0,12; 7,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,57</t>
+          <t>-1,46; 4,4</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,12</t>
+          <t>-0,61; 5,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,21</t>
+          <t>-0,0; 6,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,58</t>
+          <t>-3,62; 1,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,98</t>
+          <t>-3,27; 2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,39</t>
+          <t>-1,56; 2,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,47</t>
+          <t>-0,85; 3,64</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 658,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 1154,81</t>
+          <t>-63,41; —</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,7</t>
+          <t>-4,76; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 6,55</t>
+          <t>-2,94; 6,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,04</t>
+          <t>0,9; 8,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,73</t>
+          <t>-0,46; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,37</t>
+          <t>-0,58; 4,51</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,0</t>
+          <t>-9,11; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,0</t>
+          <t>-4,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,95</t>
+          <t>0,39; 3,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,68</t>
+          <t>0,42; 3,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,5</t>
+          <t>-0,35; 2,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,31</t>
+          <t>-0,67; 2,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,7</t>
+          <t>0,38; 2,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,39</t>
+          <t>0,18; 2,34</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2006,67</t>
+          <t>-25,91; 1758,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 1834,71</t>
+          <t>-13,64; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 691,21</t>
+          <t>-35,78; 1085,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-62,26; 739,84</t>
+          <t>-64,91; 600,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,99; 686,63</t>
+          <t>15,05; 710,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,89; 590,28</t>
+          <t>2,82; 678,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>3,76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,24</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,0</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>-0,95; 10,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>-5,96; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,41</t>
+          <t>0,28; 7,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,41</t>
+          <t>-1,04; 4,37</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>326,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>2,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,13</t>
+          <t>0,0; 8,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,82</t>
+          <t>0,44; 5,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,38</t>
+          <t>0,97; 7,08</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>-1,22; 10,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>-5,95; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 10,98</t>
+          <t>0,0; 10,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,0</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,04</t>
+          <t>0,08; 7,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,4</t>
+          <t>-1,45; 4,43</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>189,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189,9%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2,49</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,04</t>
+          <t>-3,97; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 6,28</t>
+          <t>-3,3; 2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,6</t>
+          <t>-0,55; 5,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,9</t>
+          <t>0,07; 6,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,58</t>
+          <t>-1,52; 2,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,64</t>
+          <t>-0,83; 3,24</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-50,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-3,96%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>260,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>408,3%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-50,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,96%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,41; —</t>
+          <t>-73,44; 881,07</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,68</t>
+          <t>0,87; 8,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 6,61</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,18</t>
+          <t>-4,71; 3,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>-2,36; 7,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,7</t>
+          <t>-0,29; 4,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,51</t>
+          <t>-0,7; 4,46</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>23,38%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>133,69%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,68; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,05; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>-4,93; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,98</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1,84</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,64</t>
+          <t>-0,45; 2,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,64</t>
+          <t>-0,56; 2,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,46</t>
+          <t>0,48; 3,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,21</t>
+          <t>0,39; 3,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,64</t>
+          <t>0,4; 2,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,34</t>
+          <t>0,28; 2,35</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>118,4%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>293,92%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>282,84%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>118,4%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>86,24%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 1758,27</t>
+          <t>-50,55; 829,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,64; —</t>
+          <t>-57,94; 628,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 1085,01</t>
+          <t>-17,5; inf</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 600,94</t>
+          <t>-13,93; 1680,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,05; 710,21</t>
+          <t>26,0; 661,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,82; 678,18</t>
+          <t>13,47; 663,69</t>
         </is>
       </c>
     </row>
